--- a/quizzes/009_vehicle_inspection_knowledge_quiz--quizzes.xlsx
+++ b/quizzes/009_vehicle_inspection_knowledge_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,64 +520,76 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>vehicle_inspection_knowledge_quiz_page_1</t>
+          <t>primary_function</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>vehicle inspection knowledge quiz</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is the primary function of a vehicle inspection?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Describe the main purpose of a vehicle inspection.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>section_1</t>
+          <t>critical_safety_item</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>section 1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is the most critical safety inspection item?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>List the most important item to check during a vehicle inspection.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>recommended_frequency</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>what is the primary function of a vehicle inspection?</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What is the recommended frequency of a vehicle inspection?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Provide the best answer for the frequency of inspections.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,133 +601,157 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>inspection_frequency</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>what is the most critical safety inspection item during a vehicle inspection?</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>How often should a vehicle inspection be performed?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Choose the correct frequency of inspections.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>inspection_method</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>what is the correct frequency of a vehicle inspection?</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What is the best way to inspect a vehicle?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Describe the most effective method of inspection.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>vehicle_inspection_knowledge_quiz_page_2</t>
+          <t>correct_method</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>vehicle inspection knowledge quiz page 2</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What is the correct way to inspect a vehicle?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Provide the best answer for inspecting a vehicle.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>common_issue</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>how often should a vehicle inspection be performed?</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What is the most common issue found during a vehicle inspection?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Describe the most frequent issue found during a vehicle inspection.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>inspection_effectiveness</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>what is the best way to inspect a vehicle?</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>What is the most effective way to identify issues during a vehicle inspection?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Describe the best method for detecting defects.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>inspection_sequence</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>what is the correct way to inspect a vehicle?</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What is the correct sequence of steps for a vehicle inspection?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>List the most effective sequence of inspections.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,87 +763,103 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_7</t>
+          <t>critical_component</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>what is the correct frequency of a vehicle inspection?</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What is the most critical component to check during a vehicle inspection?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Identify the key component that affects vehicle safety.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_8</t>
+          <t>defect_report</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>what is the correct way to inspect a vehicle?</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>How do you report any defects or issues found during a vehicle inspection?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Describe the process of reporting defects.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question_9</t>
+          <t>final_step</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>what is the correct frequency of a vehicle inspection?</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What is the final step in the vehicle inspection process?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Describe the last step of the inspection process.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question_10</t>
+          <t>follow_up_action</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>what is the correct way to inspect a vehicle?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>What is the recommended action to take after completing a vehicle inspection?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Provide the best course of action after an inspection.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,41 +871,130 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>question_11</t>
+          <t>inspection_scheduling</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>what is the correct frequency of a vehicle inspection?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>What is the most important factor to consider when scheduling a vehicle inspection?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Identify the key factor to consider for scheduling.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>question_12</t>
+          <t>safe_operation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>what is the correct way to inspect a vehicle?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>What is the correct method for inspecting a vehicle for safety?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Describe the safe inspection method.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>inspection_safety</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>What is the most effective way to ensure a vehicle is safe to operate?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Provide the best answer for vehicle safety.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>inspection_report</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>What is the role of a vehicle inspection report in the vehicle maintenance process?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Describe the importance of the inspection report.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>purpose_inspection</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>What is the purpose of regular vehicle inspections for safety and maintenance?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Describe the main reason for regular inspections.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -868,12 +1009,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -896,143 +1037,143 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>critical_safety_item_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>brake_functionality</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Brake functionality</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>critical_safety_item_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>suspension_and_steering_system</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Suspension and steering system</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>critical_safety_item_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>engine_and_transmission</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Engine and transmission</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>critical_safety_item_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>electrical_system</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Electrical system</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>critical_safety_item_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>recommended_frequency_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>every_6_months</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Every 6 months</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>recommended_frequency_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>every_12_months</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Every 12 months</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>recommended_frequency_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>every_24_months</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Every 24 months</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>recommended_frequency_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1049,202 +1190,355 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>inspection_frequency_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>inspection_frequency_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>inspection_frequency_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>inspection_frequency_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>inspection_frequency_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>inspection_frequency_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>correct_method_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>visual_inspection</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Visual inspection</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>correct_method_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>physical_inspection</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Physical inspection</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>correct_method_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>critical_component_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>brake_system</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Brake system</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>critical_component_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>suspension_and_steering_system</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Suspension and steering system</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>critical_component_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>engine_and_transmission</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Engine and transmission</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>critical_component_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>electrical_system</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Electrical system</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>critical_component_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>other</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>inspection_scheduling_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>vehicle_age</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Vehicle age</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>inspection_scheduling_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>vehicle_mileage</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Vehicle mileage</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>inspection_scheduling_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>vehicle_condition</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Vehicle condition</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>inspection_scheduling_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>safe_operation_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>visual_inspection</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Visual inspection</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>safe_operation_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>physical_inspection</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Physical inspection</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>safe_operation_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
